--- a/DemoBlaze/src/test/resources/Book1.xlsx
+++ b/DemoBlaze/src/test/resources/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TestNG_Programs\DemoBlaze\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{100C8613-40A4-4D9D-9E8E-8BC79D071BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F15E9D5-455C-4A9B-A679-F864B2089D4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1EF9C875-B9A8-461D-A55A-A3EDB786A7BF}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>username</t>
   </si>
@@ -42,16 +42,16 @@
     <t>password</t>
   </si>
   <si>
-    <t>anandkumar@gmail.com</t>
-  </si>
-  <si>
-    <t>Anandkumar@123</t>
-  </si>
-  <si>
-    <t>Anandkumar@gmail.com</t>
-  </si>
-  <si>
-    <t>anandkumar@123</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>CaptainAmerica</t>
+  </si>
+  <si>
+    <t>ca@gmail.com</t>
+  </si>
+  <si>
+    <t>Ca@20045678</t>
   </si>
 </sst>
 </file>
@@ -414,53 +414,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B83B7B5E-9258-4A45-ADA6-D1F1982D7ABF}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>3</v>
-      </c>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{85174FB1-46B4-49E6-92D2-A34FF3B81FB0}"/>
+    <hyperlink ref="A2" r:id="rId1" display="anandkumar@gmail.com" xr:uid="{85174FB1-46B4-49E6-92D2-A34FF3B81FB0}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{A5F251EC-77F1-42DC-9A91-3031AAC364C2}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5F440089-181F-4245-AE00-C9972FFE24B2}"/>
-    <hyperlink ref="B3" r:id="rId4" xr:uid="{AD440726-0555-4D83-A69A-528B5257370B}"/>
-    <hyperlink ref="A4" r:id="rId5" xr:uid="{1C1D1E81-1CF4-4134-AAF5-4F482DE3BCE6}"/>
-    <hyperlink ref="B4" r:id="rId6" xr:uid="{E2E349B4-989C-49A6-AB5B-574DE583A1AD}"/>
+    <hyperlink ref="C2" r:id="rId3" xr:uid="{BD17B4B9-98D4-4F20-A2C9-7022085ED156}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
